--- a/nr-update-valueset/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-organization.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:32:05+00:00</t>
+    <t>2024-03-06T16:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-update-valueset/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$224</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7248" uniqueCount="737">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2070,91 +2070,6 @@
   </si>
   <si>
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
-  &lt;code value="MSSANTE"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -2714,7 +2629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ237"/>
+  <dimension ref="A1:AJ224"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -23947,7 +23862,7 @@
         <v>661</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23958,10 +23873,10 @@
         <v>74</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>73</v>
@@ -23970,16 +23885,20 @@
         <v>73</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>96</v>
+        <v>662</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>97</v>
+        <v>663</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N208" s="2"/>
-      <c r="O208" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="P208" t="s" s="2">
         <v>73</v>
       </c>
@@ -24027,38 +23946,38 @@
         <v>73</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>99</v>
+        <v>661</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>73</v>
+        <v>667</v>
       </c>
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>73</v>
@@ -24067,21 +23986,23 @@
         <v>73</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>102</v>
+        <v>669</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>103</v>
+        <v>670</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>104</v>
+        <v>671</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O209" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>73</v>
       </c>
@@ -24117,43 +24038,41 @@
         <v>73</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>109</v>
+        <v>668</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>110</v>
+        <v>323</v>
       </c>
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
         <v>73</v>
       </c>
@@ -24174,13 +24093,13 @@
         <v>73</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>624</v>
+        <v>96</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>625</v>
+        <v>97</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -24231,38 +24150,38 @@
         <v>73</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>73</v>
@@ -24274,15 +24193,17 @@
         <v>73</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N211" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>73</v>
@@ -24319,39 +24240,39 @@
         <v>73</v>
       </c>
       <c r="AB211" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC211" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD211" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE211" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24362,7 +24283,7 @@
         <v>74</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>73</v>
@@ -24371,18 +24292,20 @@
         <v>73</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>679</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>73</v>
@@ -24419,39 +24342,39 @@
         <v>73</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>109</v>
+        <v>680</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>93</v>
+        <v>681</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24459,7 +24382,7 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G213" t="s" s="2">
         <v>81</v>
@@ -24471,19 +24394,19 @@
         <v>73</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
         <v>128</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>205</v>
+        <v>683</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>206</v>
+        <v>684</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>207</v>
+        <v>685</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -24491,7 +24414,7 @@
       </c>
       <c r="Q213" s="2"/>
       <c r="R213" t="s" s="2">
-        <v>670</v>
+        <v>73</v>
       </c>
       <c r="S213" t="s" s="2">
         <v>73</v>
@@ -24509,13 +24432,13 @@
         <v>73</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>73</v>
+        <v>686</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>73</v>
+        <v>474</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>73</v>
@@ -24533,27 +24456,27 @@
         <v>73</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>209</v>
+        <v>687</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24573,18 +24496,20 @@
         <v>73</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>140</v>
+        <v>271</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>213</v>
+        <v>689</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>691</v>
+      </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>73</v>
@@ -24594,7 +24519,7 @@
         <v>73</v>
       </c>
       <c r="S214" t="s" s="2">
-        <v>673</v>
+        <v>73</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>73</v>
@@ -24609,11 +24534,13 @@
         <v>73</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y214" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y214" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z214" t="s" s="2">
-        <v>674</v>
+        <v>73</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>73</v>
@@ -24631,7 +24558,7 @@
         <v>73</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>215</v>
+        <v>692</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>74</v>
@@ -24648,14 +24575,12 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>676</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
         <v>73</v>
       </c>
@@ -24667,24 +24592,26 @@
         <v>81</v>
       </c>
       <c r="H215" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I215" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J215" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I215" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J215" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K215" t="s" s="2">
-        <v>677</v>
+        <v>96</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N215" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>73</v>
@@ -24733,27 +24660,27 @@
         <v>73</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>109</v>
+        <v>697</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>626</v>
+        <v>698</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24761,10 +24688,10 @@
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>73</v>
@@ -24773,21 +24700,23 @@
         <v>73</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>162</v>
+        <v>699</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>627</v>
+        <v>700</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>628</v>
+        <v>701</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>702</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>73</v>
       </c>
@@ -24796,7 +24725,7 @@
         <v>73</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>681</v>
+        <v>73</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>73</v>
@@ -24811,13 +24740,13 @@
         <v>73</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>629</v>
+        <v>73</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>630</v>
+        <v>73</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>73</v>
@@ -24835,16 +24764,16 @@
         <v>73</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>631</v>
+        <v>698</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>632</v>
+        <v>93</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>94</v>
@@ -24852,10 +24781,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>682</v>
+        <v>704</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>633</v>
+        <v>704</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24863,35 +24792,31 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G217" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K217" t="s" s="2">
         <v>96</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>683</v>
+        <v>97</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N217" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>73</v>
       </c>
@@ -24939,7 +24864,7 @@
         <v>73</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>638</v>
+        <v>99</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>74</v>
@@ -24948,54 +24873,52 @@
         <v>81</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>639</v>
+        <v>705</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I218" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>640</v>
+        <v>103</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>641</v>
+        <v>104</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>73</v>
       </c>
@@ -25019,85 +24942,87 @@
         <v>73</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>644</v>
+        <v>73</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>645</v>
+        <v>73</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>646</v>
+        <v>109</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI218" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>647</v>
+        <v>706</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>73</v>
+        <v>707</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I219" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J219" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>648</v>
+        <v>102</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>649</v>
+        <v>708</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O219" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="O219" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>73</v>
       </c>
@@ -25145,27 +25070,27 @@
         <v>73</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>652</v>
+        <v>710</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>653</v>
+        <v>711</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -25185,21 +25110,23 @@
         <v>73</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>212</v>
+        <v>290</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>654</v>
+        <v>712</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>655</v>
+        <v>713</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O220" s="2"/>
+        <v>714</v>
+      </c>
+      <c r="O220" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>73</v>
       </c>
@@ -25223,13 +25150,13 @@
         <v>73</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>73</v>
+        <v>716</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>73</v>
+        <v>717</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>73</v>
@@ -25247,7 +25174,7 @@
         <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
@@ -25259,15 +25186,15 @@
         <v>93</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25278,10 +25205,10 @@
         <v>74</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>73</v>
@@ -25290,19 +25217,19 @@
         <v>73</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>689</v>
+        <v>719</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>692</v>
+        <v>722</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>693</v>
+        <v>723</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>73</v>
@@ -25351,27 +25278,27 @@
         <v>73</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>694</v>
+        <v>94</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25382,7 +25309,7 @@
         <v>74</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>73</v>
@@ -25391,22 +25318,20 @@
         <v>73</v>
       </c>
       <c r="J222" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>696</v>
+        <v>612</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>699</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>700</v>
+        <v>726</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>73</v>
@@ -25455,27 +25380,27 @@
         <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>323</v>
+        <v>727</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25498,16 +25423,20 @@
         <v>73</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>96</v>
+        <v>729</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>97</v>
+        <v>730</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P223" t="s" s="2">
         <v>73</v>
       </c>
@@ -25555,7 +25484,7 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>99</v>
+        <v>728</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
@@ -25564,22 +25493,22 @@
         <v>81</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
@@ -25589,7 +25518,7 @@
         <v>75</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>73</v>
@@ -25598,18 +25527,20 @@
         <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>102</v>
+        <v>733</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>103</v>
+        <v>734</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>104</v>
+        <v>735</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O224" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O224" t="s" s="2">
+        <v>736</v>
+      </c>
       <c r="P224" t="s" s="2">
         <v>73</v>
       </c>
@@ -25645,19 +25576,19 @@
         <v>73</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC224" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD224" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE224" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>109</v>
+        <v>732</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
@@ -25669,1347 +25600,11 @@
         <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="225" hidden="true">
-      <c r="A225" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="C225" s="2"/>
-      <c r="D225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G225" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J225" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K225" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L225" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="O225" s="2"/>
-      <c r="P225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q225" s="2"/>
-      <c r="R225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF225" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH225" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI225" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AJ225" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="226" hidden="true">
-      <c r="A226" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C226" s="2"/>
-      <c r="D226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E226" s="2"/>
-      <c r="F226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J226" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K226" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="L226" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="O226" s="2"/>
-      <c r="P226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q226" s="2"/>
-      <c r="R226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X226" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y226" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="Z226" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF226" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AG226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI226" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ226" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="227" hidden="true">
-      <c r="A227" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E227" s="2"/>
-      <c r="F227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J227" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K227" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="L227" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O227" s="2"/>
-      <c r="P227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q227" s="2"/>
-      <c r="R227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF227" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AG227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI227" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ227" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="228" hidden="true">
-      <c r="A228" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C228" s="2"/>
-      <c r="D228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E228" s="2"/>
-      <c r="F228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J228" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K228" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L228" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O228" s="2"/>
-      <c r="P228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q228" s="2"/>
-      <c r="R228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF228" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AG228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI228" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ228" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="229" hidden="true">
-      <c r="A229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E229" s="2"/>
-      <c r="F229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G229" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K229" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="P229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q229" s="2"/>
-      <c r="R229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AG229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH229" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI229" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ229" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="230" hidden="true">
-      <c r="A230" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C230" s="2"/>
-      <c r="D230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K230" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L230" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N230" s="2"/>
-      <c r="O230" s="2"/>
-      <c r="P230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q230" s="2"/>
-      <c r="R230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF230" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ230" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="231" hidden="true">
-      <c r="A231" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C231" s="2"/>
-      <c r="D231" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="E231" s="2"/>
-      <c r="F231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K231" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L231" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O231" s="2"/>
-      <c r="P231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q231" s="2"/>
-      <c r="R231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI231" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ231" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="232" hidden="true">
-      <c r="A232" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C232" s="2"/>
-      <c r="D232" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I232" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J232" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K232" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L232" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="P232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q232" s="2"/>
-      <c r="R232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF232" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AG232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI232" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ232" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="233" hidden="true">
-      <c r="A233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C233" s="2"/>
-      <c r="D233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K233" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="L233" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="P233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q233" s="2"/>
-      <c r="R233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X233" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="Z233" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AA233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AG233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI233" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ233" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="234" hidden="true">
-      <c r="A234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C234" s="2"/>
-      <c r="D234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G234" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K234" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="L234" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="N234" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="P234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q234" s="2"/>
-      <c r="R234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="AG234" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH234" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI234" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ234" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="235" hidden="true">
-      <c r="A235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="C235" s="2"/>
-      <c r="D235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G235" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K235" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="L235" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N235" s="2"/>
-      <c r="O235" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="P235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q235" s="2"/>
-      <c r="R235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="AG235" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH235" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI235" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ235" t="s" s="2">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="236" hidden="true">
-      <c r="A236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="C236" s="2"/>
-      <c r="D236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E236" s="2"/>
-      <c r="F236" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K236" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="L236" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="P236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q236" s="2"/>
-      <c r="R236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="AG236" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI236" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ236" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="237" hidden="true">
-      <c r="A237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="C237" s="2"/>
-      <c r="D237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E237" s="2"/>
-      <c r="F237" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G237" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H237" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K237" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="P237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q237" s="2"/>
-      <c r="R237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ237">
+  <autoFilter ref="A1:AJ224">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27019,7 +25614,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI236">
+  <conditionalFormatting sqref="A2:AI223">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-valueset/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
